--- a/02_Zero_Shot/outputs/Embedding/RoBERTa-base/RESULT_clap_roberta-base_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/RoBERTa-base/RESULT_clap_roberta-base_zeroshot.xlsx
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.681309583000257</v>
+        <v>28.85458829699928</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001893769861000085</v>
+        <v>0.009618196098999761</v>
       </c>
     </row>
   </sheetData>
